--- a/data/trans_orig/P15A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15445</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256290</t>
+          <t>256587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268394</t>
+          <t>268386</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245393</t>
+          <t>246664</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257956</t>
+          <t>257993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>506889</t>
+          <t>507361</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>524557</t>
+          <t>524347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15327</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15914</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477748</t>
+          <t>477511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489991</t>
+          <t>489969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488035</t>
+          <t>487017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499890</t>
+          <t>499360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>969999</t>
+          <t>970251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987368</t>
+          <t>987137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289744</t>
+          <t>289441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308028</t>
+          <t>308087</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325050</t>
+          <t>324205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334272</t>
+          <t>334288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620202</t>
+          <t>621285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640476</t>
+          <t>640427</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331722</t>
+          <t>331839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347883</t>
+          <t>347559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353574</t>
+          <t>353919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366140</t>
+          <t>366378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691847</t>
+          <t>689905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>711300</t>
+          <t>710887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24112</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189306</t>
+          <t>188879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200214</t>
+          <t>200440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191831</t>
+          <t>191414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204562</t>
+          <t>204614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386864</t>
+          <t>386389</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401990</t>
+          <t>402083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>18199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>18783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30383</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253347</t>
+          <t>252612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267002</t>
+          <t>266756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259846</t>
+          <t>259361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272907</t>
+          <t>272899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>518572</t>
+          <t>518031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536820</t>
+          <t>537295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39449</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,47 +2806,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>18415</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>10861</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>27410</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>18415</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>11150</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>28876</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33284</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61413</t>
+          <t>61287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>575578</t>
+          <t>576601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597257</t>
+          <t>597330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,47 +2919,47 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>619804</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>610809</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>627358</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>97,11%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>619804</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>609343</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>627069</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1191833</t>
+          <t>1191959</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1219962</t>
+          <t>1219277</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69790</t>
+          <t>70732</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>704853</t>
+          <t>705184</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726550</t>
+          <t>726398</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>744280</t>
+          <t>745095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>765139</t>
+          <t>765179</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1457516</t>
+          <t>1456574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1487260</t>
+          <t>1486193</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>102111</t>
+          <t>103130</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>75267</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>115059</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>189848</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>251213</t>
+          <t>249424</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3131688</t>
+          <t>3129453</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3174432</t>
+          <t>3173413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3264138</t>
+          <t>3263132</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3303909</t>
+          <t>3303930</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6404528</t>
+          <t>6406317</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6465893</t>
+          <t>6464982</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20791</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30735</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273947</t>
+          <t>275047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287827</t>
+          <t>288100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272657</t>
+          <t>272445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284386</t>
+          <t>284506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>551248</t>
+          <t>552908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569900</t>
+          <t>570752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486467</t>
+          <t>486515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500554</t>
+          <t>499763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509648</t>
+          <t>509084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520645</t>
+          <t>520620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998664</t>
+          <t>999918</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018343</t>
+          <t>1018342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27441</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299966</t>
+          <t>300806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315430</t>
+          <t>314861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313579</t>
+          <t>312446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330971</t>
+          <t>331011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>619241</t>
+          <t>618997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642400</t>
+          <t>642862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>33344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349511</t>
+          <t>348477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366300</t>
+          <t>366537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375574</t>
+          <t>374966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386088</t>
+          <t>385919</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730091</t>
+          <t>729589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750577</t>
+          <t>749514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199056</t>
+          <t>198210</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209726</t>
+          <t>209567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203125</t>
+          <t>203494</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215413</t>
+          <t>215414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406063</t>
+          <t>406172</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422506</t>
+          <t>422281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>36068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258510</t>
+          <t>258085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271173</t>
+          <t>271108</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253943</t>
+          <t>253555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269764</t>
+          <t>270736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>518334</t>
+          <t>517944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538730</t>
+          <t>538424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30180</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31097</t>
+          <t>29331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58022</t>
+          <t>56145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>629255</t>
+          <t>627489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649160</t>
+          <t>647228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663673</t>
+          <t>663948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681801</t>
+          <t>681916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1298619</t>
+          <t>1300496</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1325544</t>
+          <t>1327310</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24429</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>761060</t>
+          <t>761172</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775086</t>
+          <t>775063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>799424</t>
+          <t>799678</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815644</t>
+          <t>816077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1566949</t>
+          <t>1567362</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588142</t>
+          <t>1588687</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122151</t>
+          <t>120595</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>79889</t>
+          <t>78736</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>120306</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>167014</t>
+          <t>169870</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>226559</t>
+          <t>228695</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3304628</t>
+          <t>3306184</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3346763</t>
+          <t>3346604</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3438003</t>
+          <t>3439157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3478420</t>
+          <t>3479573</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6758529</t>
+          <t>6756393</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6818074</t>
+          <t>6815218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25622</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280491</t>
+          <t>281249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291154</t>
+          <t>291752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271532</t>
+          <t>271980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284299</t>
+          <t>284773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556842</t>
+          <t>557465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>573686</t>
+          <t>574063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>19431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489301</t>
+          <t>490012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500480</t>
+          <t>500490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512347</t>
+          <t>513246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521815</t>
+          <t>522075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007738</t>
+          <t>1006228</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020520</t>
+          <t>1019573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297840</t>
+          <t>297757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311658</t>
+          <t>311970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324704</t>
+          <t>323992</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334394</t>
+          <t>333647</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626940</t>
+          <t>627315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643681</t>
+          <t>643365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>30545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343605</t>
+          <t>342897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360657</t>
+          <t>360014</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357300</t>
+          <t>356738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376645</t>
+          <t>376245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706521</t>
+          <t>705432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731917</t>
+          <t>732499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199861</t>
+          <t>199259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209283</t>
+          <t>209264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209588</t>
+          <t>208629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217532</t>
+          <t>217527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412344</t>
+          <t>413328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425702</t>
+          <t>425136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36785</t>
+          <t>36821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>29399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54890</t>
+          <t>55153</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>238914</t>
+          <t>239978</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254278</t>
+          <t>254750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236330</t>
+          <t>236294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256251</t>
+          <t>255681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481348</t>
+          <t>481085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>506555</t>
+          <t>506839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639818</t>
+          <t>639600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653382</t>
+          <t>653286</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>678616</t>
+          <t>677546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689447</t>
+          <t>689238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1324021</t>
+          <t>1323937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340816</t>
+          <t>1340528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>24896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>46982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750940</t>
+          <t>750838</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767837</t>
+          <t>767129</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>801317</t>
+          <t>801271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817550</t>
+          <t>817910</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1558357</t>
+          <t>1557768</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1582557</t>
+          <t>1581281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>72684</t>
+          <t>71065</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>108185</t>
+          <t>108483</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71030</t>
+          <t>69056</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110136</t>
+          <t>107560</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>150790</t>
+          <t>152738</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>205997</t>
+          <t>206076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3286165</t>
+          <t>3285867</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3321666</t>
+          <t>3323285</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3434406</t>
+          <t>3436982</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3473512</t>
+          <t>3475486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6732895</t>
+          <t>6732816</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6788102</t>
+          <t>6786154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>14570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14517</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296408</t>
+          <t>296873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307577</t>
+          <t>307706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271451</t>
+          <t>271368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281243</t>
+          <t>281414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572961</t>
+          <t>572404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>586560</t>
+          <t>586343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>43705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493254</t>
+          <t>494193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>513106</t>
+          <t>512823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490920</t>
+          <t>491352</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504581</t>
+          <t>504363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>991660</t>
+          <t>989654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015483</t>
+          <t>1014111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304404</t>
+          <t>305026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313425</t>
+          <t>313791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334834</t>
+          <t>334496</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343980</t>
+          <t>343581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643035</t>
+          <t>642759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655578</t>
+          <t>655485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21286</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29782</t>
+          <t>30778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291271</t>
+          <t>291796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310755</t>
+          <t>310774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454730</t>
+          <t>456485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473300</t>
+          <t>473092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758492</t>
+          <t>757496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783009</t>
+          <t>782564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172736</t>
+          <t>172561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178218</t>
+          <t>178207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205687</t>
+          <t>205394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381046</t>
+          <t>380592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386852</t>
+          <t>386849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19923</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251631</t>
+          <t>252282</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263558</t>
+          <t>264109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237133</t>
+          <t>237598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247624</t>
+          <t>247888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493986</t>
+          <t>495348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509235</t>
+          <t>509411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>32320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19132</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>47139</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602604</t>
+          <t>602889</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617219</t>
+          <t>617114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>818685</t>
+          <t>816945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840465</t>
+          <t>840652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1427966</t>
+          <t>1426405</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1454152</t>
+          <t>1454412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27946</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42061</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>900774</t>
+          <t>901723</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923283</t>
+          <t>922934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696589</t>
+          <t>696250</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709711</t>
+          <t>709263</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1604391</t>
+          <t>1604014</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1629848</t>
+          <t>1630794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54522</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97424</t>
+          <t>97446</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73012</t>
+          <t>71915</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114774</t>
+          <t>111038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>134783</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>193208</t>
+          <t>191295</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3362393</t>
+          <t>3362371</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3405295</t>
+          <t>3407103</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3547383</t>
+          <t>3551119</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3589145</t>
+          <t>3590242</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6928766</t>
+          <t>6930679</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6987191</t>
+          <t>6988215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>16442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>26945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256587</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268386</t>
+          <t>268310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246664</t>
+          <t>245054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257993</t>
+          <t>257964</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>507361</t>
+          <t>506903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>524347</t>
+          <t>523828</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8964</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15932</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8964</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4589</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16932</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26773</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477511</t>
+          <t>477381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>489969</t>
+          <t>490028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,47 +1204,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>494985</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>488017</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>499943</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>96,84%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>494985</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>487017</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>499360</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>970251</t>
+          <t>969793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>987137</t>
+          <t>986854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>28777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289441</t>
+          <t>290069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308087</t>
+          <t>307216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324205</t>
+          <t>325321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334288</t>
+          <t>334279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621285</t>
+          <t>617896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640427</t>
+          <t>639703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>18643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>38278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331839</t>
+          <t>330633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347559</t>
+          <t>346990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353919</t>
+          <t>353629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366378</t>
+          <t>366946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689905</t>
+          <t>691849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710887</t>
+          <t>711484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16254</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188879</t>
+          <t>188292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200440</t>
+          <t>200324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191414</t>
+          <t>191078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204614</t>
+          <t>204637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386389</t>
+          <t>386892</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402083</t>
+          <t>403047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>28715</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252612</t>
+          <t>253339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266756</t>
+          <t>266901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259361</t>
+          <t>258883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272899</t>
+          <t>272591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>518031</t>
+          <t>520240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>537295</t>
+          <t>537566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27410</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>33449</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61287</t>
+          <t>61016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576601</t>
+          <t>575902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597330</t>
+          <t>597920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>610809</t>
+          <t>610688</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>627358</t>
+          <t>627281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1191959</t>
+          <t>1192230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1219277</t>
+          <t>1219797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17397</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41113</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70732</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>705184</t>
+          <t>705503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726398</t>
+          <t>726401</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>745095</t>
+          <t>744746</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>765179</t>
+          <t>765788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1456574</t>
+          <t>1457263</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1486193</t>
+          <t>1486717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>103130</t>
+          <t>102848</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>146963</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>75267</t>
+          <t>75895</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>113942</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>249424</t>
+          <t>247827</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3129453</t>
+          <t>3129580</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3173413</t>
+          <t>3173695</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3263132</t>
+          <t>3265255</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3303930</t>
+          <t>3303302</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6406317</t>
+          <t>6407914</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6464982</t>
+          <t>6465343</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>15449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29075</t>
+          <t>29755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275047</t>
+          <t>274169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288100</t>
+          <t>288150</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272445</t>
+          <t>271796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284506</t>
+          <t>284764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552908</t>
+          <t>552228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>570752</t>
+          <t>569772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>27965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486515</t>
+          <t>485746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499763</t>
+          <t>499756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509084</t>
+          <t>509010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520620</t>
+          <t>520638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999918</t>
+          <t>1001327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018342</t>
+          <t>1019118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28574</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>45755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300806</t>
+          <t>299735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314861</t>
+          <t>314840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312446</t>
+          <t>314048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331011</t>
+          <t>331080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618997</t>
+          <t>619311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642862</t>
+          <t>641986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33344</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>348477</t>
+          <t>350201</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366537</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>374966</t>
+          <t>374265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385919</t>
+          <t>386063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>729589</t>
+          <t>730525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749514</t>
+          <t>749522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14408</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198210</t>
+          <t>197910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209567</t>
+          <t>209432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203494</t>
+          <t>202306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215414</t>
+          <t>214764</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>406172</t>
+          <t>405300</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422281</t>
+          <t>422386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15896</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258085</t>
+          <t>259247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271108</t>
+          <t>271266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253555</t>
+          <t>250537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270736</t>
+          <t>269704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>517944</t>
+          <t>518211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538424</t>
+          <t>538815</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>29410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29331</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56145</t>
+          <t>56753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>627489</t>
+          <t>628068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647228</t>
+          <t>647686</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>663948</t>
+          <t>664443</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681916</t>
+          <t>681790</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1300496</t>
+          <t>1299888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1327310</t>
+          <t>1326069</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35589</t>
+          <t>34569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>761172</t>
+          <t>760427</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775063</t>
+          <t>774932</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>799678</t>
+          <t>800289</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>816077</t>
+          <t>816355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1567362</t>
+          <t>1568382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588687</t>
+          <t>1588764</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>78985</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120595</t>
+          <t>119930</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>78736</t>
+          <t>80274</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>119152</t>
+          <t>120256</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>169870</t>
+          <t>168303</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>228695</t>
+          <t>227313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3306184</t>
+          <t>3306849</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3346604</t>
+          <t>3347794</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3439157</t>
+          <t>3438053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3479573</t>
+          <t>3478035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6756393</t>
+          <t>6757775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6815218</t>
+          <t>6816785</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281249</t>
+          <t>281001</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291752</t>
+          <t>291430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271980</t>
+          <t>270854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284773</t>
+          <t>284461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557465</t>
+          <t>557221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574063</t>
+          <t>573440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12563</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490012</t>
+          <t>490016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500490</t>
+          <t>500465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513246</t>
+          <t>511972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522075</t>
+          <t>521998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1006228</t>
+          <t>1006905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019573</t>
+          <t>1020497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297757</t>
+          <t>298183</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311970</t>
+          <t>311503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323992</t>
+          <t>324422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333647</t>
+          <t>334193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627315</t>
+          <t>627020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643365</t>
+          <t>643566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51815</t>
+          <t>49221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342897</t>
+          <t>342186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360014</t>
+          <t>359873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356738</t>
+          <t>356820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376245</t>
+          <t>376389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>705432</t>
+          <t>708026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732499</t>
+          <t>733013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199259</t>
+          <t>199930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209264</t>
+          <t>209285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208629</t>
+          <t>209486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217527</t>
+          <t>217533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>413328</t>
+          <t>411166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425136</t>
+          <t>425239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>24316</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>29715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55153</t>
+          <t>56450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239978</t>
+          <t>238807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>254750</t>
+          <t>254013</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236294</t>
+          <t>236970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255681</t>
+          <t>256695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481085</t>
+          <t>479788</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>506839</t>
+          <t>506523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>639600</t>
+          <t>640467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>653286</t>
+          <t>653375</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>677546</t>
+          <t>678208</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689238</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323937</t>
+          <t>1323456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340528</t>
+          <t>1339968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>28290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24896</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46982</t>
+          <t>46374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>750838</t>
+          <t>750293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767129</t>
+          <t>767536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>801271</t>
+          <t>801571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817910</t>
+          <t>817840</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1557768</t>
+          <t>1558376</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1581281</t>
+          <t>1581039</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71065</t>
+          <t>70895</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>108483</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>69712</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107560</t>
+          <t>110150</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>152632</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>206076</t>
+          <t>205724</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3285867</t>
+          <t>3285546</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3323285</t>
+          <t>3323455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3436982</t>
+          <t>3434392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3475486</t>
+          <t>3474830</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6732816</t>
+          <t>6733168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6786154</t>
+          <t>6786260</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,102 +10697,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14570</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13265</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8809</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>19025</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>21975</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>15187</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>29697</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12374</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8221</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18267</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>20287</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>14734</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>28673</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -10810,102 +10810,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303531</t>
+          <t>310134</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296873</t>
+          <t>303442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307706</t>
+          <t>314415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>302796</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>297036</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>307252</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>612931</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>605209</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>619719</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>95,32%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>277261</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>271368</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>281414</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>580790</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>572404</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>586343</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43705</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>506592</t>
+          <t>518767</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494193</t>
+          <t>506942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512823</t>
+          <t>525032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>498855</t>
+          <t>529908</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491352</t>
+          <t>521575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504363</t>
+          <t>535635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1005447</t>
+          <t>1048675</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>989654</t>
+          <t>1035009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014111</t>
+          <t>1058129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14632</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>310283</t>
+          <t>309087</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305026</t>
+          <t>302419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313791</t>
+          <t>312836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>340080</t>
+          <t>347310</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334496</t>
+          <t>341755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343581</t>
+          <t>350910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>650364</t>
+          <t>656398</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642759</t>
+          <t>648638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655485</t>
+          <t>662005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>34552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>305317</t>
+          <t>362893</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291796</t>
+          <t>347771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310774</t>
+          <t>369692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>468945</t>
+          <t>414632</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>456485</t>
+          <t>400364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473092</t>
+          <t>419053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>774261</t>
+          <t>777526</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757496</t>
+          <t>760555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>782564</t>
+          <t>787046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176545</t>
+          <t>203237</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172561</t>
+          <t>198318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178207</t>
+          <t>205144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>208116</t>
+          <t>226690</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205394</t>
+          <t>224318</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>384661</t>
+          <t>429926</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>380592</t>
+          <t>425372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386849</t>
+          <t>431984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>15832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259984</t>
+          <t>261544</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252282</t>
+          <t>254875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264109</t>
+          <t>265269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>243575</t>
+          <t>249744</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237598</t>
+          <t>243517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247888</t>
+          <t>254117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>503559</t>
+          <t>511288</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>495348</t>
+          <t>502708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509411</t>
+          <t>517220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13114</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8613</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32320</t>
+          <t>33474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>39241</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47139</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>611165</t>
+          <t>703727</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602889</t>
+          <t>693235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617114</t>
+          <t>710263</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>829332</t>
+          <t>748776</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>816945</t>
+          <t>738583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840652</t>
+          <t>756117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1440497</t>
+          <t>1452503</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1426405</t>
+          <t>1437980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1454412</t>
+          <t>1462974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>17045</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>15374</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>32418</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>22288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42438</t>
+          <t>45831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>913470</t>
+          <t>781027</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>901723</t>
+          <t>767142</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922934</t>
+          <t>788189</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>704508</t>
+          <t>815957</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696250</t>
+          <t>806655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709263</t>
+          <t>822169</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1617979</t>
+          <t>1596985</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1604014</t>
+          <t>1583572</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1630794</t>
+          <t>1607115</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>72930</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>97446</t>
+          <t>107011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,67 +13476,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>99438</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71915</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111038</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>181781</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>156515</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>211970</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>164416</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>133759</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>191295</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3386887</t>
+          <t>3450419</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3362371</t>
+          <t>3425751</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3407103</t>
+          <t>3467636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,67 +13589,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3570671</t>
+          <t>3635813</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3551119</t>
+          <t>3615639</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3590242</t>
+          <t>3652424</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>7086232</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>7056043</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>7111498</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>97,5%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>8503</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6957558</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6930679</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6988215</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
